--- a/whatsapp/layout/prueba.xlsx
+++ b/whatsapp/layout/prueba.xlsx
@@ -8,24 +8,35 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/joss/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC9B9A49-D628-C743-832A-84D8F4B59162}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F064CEF0-F421-1D46-8303-07336004A92E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="680" windowWidth="20500" windowHeight="17420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="31">
   <si>
     <t>Rank</t>
   </si>
@@ -60,43 +71,64 @@
     <t>PPB SA</t>
   </si>
   <si>
-    <t>Ocupación</t>
-  </si>
-  <si>
-    <t>Coyote vs. Acme</t>
-  </si>
-  <si>
-    <t>Hechizo de Amor 2: La Magia Continua</t>
-  </si>
-  <si>
     <t/>
-  </si>
-  <si>
-    <t>Cars (20 Aniversario)</t>
-  </si>
-  <si>
-    <t>Zona Cero</t>
-  </si>
-  <si>
-    <t>La Noche Del Demonio: Estan Entre Nosotros</t>
-  </si>
-  <si>
-    <t>Spider-Man: Un Nuevo Dia</t>
-  </si>
-  <si>
-    <t>El Club del Pie Izquierdo</t>
   </si>
   <si>
     <t>La Odisea</t>
   </si>
   <si>
-    <t>30° Tour de Cine Frances (2026)</t>
+    <t>Total</t>
   </si>
   <si>
-    <t>Oasis: Don't Look Back in Anger</t>
+    <t>Exclusiva Cinemex</t>
   </si>
   <si>
-    <t>Total</t>
+    <t>(Var% / Dif) Total vs 2024</t>
+  </si>
+  <si>
+    <t>2026 YTD</t>
+  </si>
+  <si>
+    <t>(Var% / Dif) Total vs 2026 YTD</t>
+  </si>
+  <si>
+    <t>Var % Sem Ant</t>
+  </si>
+  <si>
+    <t>% Ocup</t>
+  </si>
+  <si>
+    <t>Industria</t>
+  </si>
+  <si>
+    <t>Cinemex</t>
+  </si>
+  <si>
+    <t>Toy Story 5</t>
+  </si>
+  <si>
+    <t>Minions &amp; Monstruos</t>
+  </si>
+  <si>
+    <t>Moana</t>
+  </si>
+  <si>
+    <t>Evil Dead: En Llamas</t>
+  </si>
+  <si>
+    <t>La Invitacion</t>
+  </si>
+  <si>
+    <t>El Dia de la Revelacion</t>
+  </si>
+  <si>
+    <t>Obsesion</t>
+  </si>
+  <si>
+    <t>Supergirl</t>
+  </si>
+  <si>
+    <t>Backrooms: Sin Salida</t>
   </si>
 </sst>
 </file>
@@ -111,7 +143,7 @@
     <numFmt numFmtId="168" formatCode="_-&quot;$&quot;* #,##0_-;\-&quot;$&quot;* #,##0_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="169" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="34">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -306,8 +338,46 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1" tint="0.499984740745262"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1" tint="0.499984740745262"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1" tint="0.34998626667073579"/>
-      <name val="Calibri Light"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1" tint="0.34998626667073579"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1" tint="0.499984740745262"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1" tint="0.34998626667073579"/>
+      <name val="Calibri"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -493,13 +563,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1974,91 +2044,232 @@
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="167" fontId="23" fillId="0" borderId="0" xfId="44" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="23" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="185" applyFont="1"/>
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" xfId="185" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" xfId="185" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" xfId="185" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="185" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="23" fillId="0" borderId="0" xfId="185" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="23" fillId="0" borderId="0" xfId="185" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" xfId="185" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" xfId="185" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" xfId="185" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" xfId="185" applyFont="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="26" fillId="34" borderId="0" xfId="185" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="26" fillId="34" borderId="0" xfId="185" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="26" fillId="34" borderId="0" xfId="44" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" xfId="185" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="722" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="722" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="722" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="33" borderId="0" xfId="722" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="26" fillId="34" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="25" fillId="0" borderId="0" xfId="43" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="26" fillId="34" borderId="0" xfId="43" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="25" fillId="0" borderId="0" xfId="43" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="26" fillId="34" borderId="0" xfId="43" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="10" xfId="185" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="10" xfId="185" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="24" fillId="0" borderId="10" xfId="62" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="24" fillId="0" borderId="10" xfId="120" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="24" fillId="0" borderId="10" xfId="185" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="26" fillId="0" borderId="10" xfId="88" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="24" fillId="0" borderId="10" xfId="185" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="26" fillId="0" borderId="10" xfId="88" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="30" fillId="0" borderId="10" xfId="737" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="10" xfId="185" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="23" fillId="0" borderId="10" xfId="44" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="23" fillId="0" borderId="10" xfId="42" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="10" xfId="185" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="23" fillId="0" borderId="10" xfId="62" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="23" fillId="0" borderId="10" xfId="120" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="23" fillId="0" borderId="10" xfId="185" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="25" fillId="0" borderId="10" xfId="43" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="25" fillId="0" borderId="10" xfId="88" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="169" fontId="23" fillId="0" borderId="10" xfId="185" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="25" fillId="0" borderId="10" xfId="43" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="10" xfId="185" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" xfId="185" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="27" fillId="33" borderId="0" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="23" fillId="33" borderId="0" xfId="43" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="25" fillId="0" borderId="10" xfId="88" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="25" fillId="0" borderId="10" xfId="88" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="25" fillId="0" borderId="10" xfId="88" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="34" borderId="10" xfId="722" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="34" borderId="10" xfId="722" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="28" fillId="34" borderId="10" xfId="62" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="28" fillId="34" borderId="10" xfId="120" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="28" fillId="34" borderId="10" xfId="722" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="29" fillId="34" borderId="10" xfId="88" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="28" fillId="34" borderId="10" xfId="722" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="29" fillId="34" borderId="10" xfId="737" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="722" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="722" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="23" fillId="0" borderId="0" xfId="62" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="23" fillId="0" borderId="0" xfId="120" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="23" fillId="0" borderId="0" xfId="722" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="25" fillId="0" borderId="0" xfId="88" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="23" fillId="0" borderId="0" xfId="722" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="25" fillId="0" borderId="0" xfId="88" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="30" fillId="0" borderId="0" xfId="88" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="26" fillId="33" borderId="0" xfId="62" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="26" fillId="33" borderId="0" xfId="120" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="26" fillId="33" borderId="0" xfId="185" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="26" fillId="33" borderId="0" xfId="88" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="26" fillId="33" borderId="0" xfId="185" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="26" fillId="33" borderId="0" xfId="88" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="29" fillId="33" borderId="0" xfId="737" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="722" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="722" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="33" borderId="0" xfId="722" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="33" borderId="0" xfId="722" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="29" fillId="33" borderId="0" xfId="62" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="29" fillId="33" borderId="0" xfId="120" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="29" fillId="33" borderId="0" xfId="722" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="29" fillId="33" borderId="0" xfId="88" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="29" fillId="33" borderId="0" xfId="722" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="29" fillId="33" borderId="0" xfId="88" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="722" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="722" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="33" borderId="0" xfId="722" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="29" fillId="33" borderId="0" xfId="141" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="29" fillId="33" borderId="0" xfId="141" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="29" fillId="33" borderId="0" xfId="141" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="722" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="31" fillId="0" borderId="0" xfId="62" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="31" fillId="0" borderId="0" xfId="120" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="31" fillId="0" borderId="0" xfId="722" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="33" fillId="0" borderId="0" xfId="141" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="31" fillId="0" borderId="0" xfId="722" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="33" fillId="0" borderId="0" xfId="141" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="33" fillId="0" borderId="0" xfId="88" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1337">
@@ -3400,7 +3611,128 @@
     <cellStyle name="Total" xfId="15" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="13" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="24">
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -3676,559 +4008,1048 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:O32"/>
+  <dimension ref="A1:Q32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15"/>
   <cols>
     <col min="3" max="3" width="41" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:15" ht="32">
-      <c r="B2" s="7" t="s">
+    <row r="1" spans="1:17">
+      <c r="A1" s="4"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+      <c r="M1" s="4"/>
+      <c r="N1" s="5"/>
+      <c r="O1" s="6"/>
+      <c r="P1" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q1" s="7"/>
+    </row>
+    <row r="2" spans="1:17" ht="32">
+      <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="14" t="s">
+      <c r="C2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="14" t="s">
+      <c r="D2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="14" t="s">
+      <c r="E2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="14" t="s">
+      <c r="F2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="14" t="s">
+      <c r="G2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="I2" s="14" t="s">
+      <c r="H2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="J2" s="14" t="s">
+      <c r="I2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K2" s="14" t="s">
+      <c r="J2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="L2" s="14" t="s">
+      <c r="K2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="M2" s="7" t="s">
+      <c r="L2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="N2" s="14" t="s">
+      <c r="M2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="O2" s="28" t="s">
+      <c r="N2" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="O2" s="6"/>
+      <c r="P2" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q2" s="8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17">
+      <c r="A3" s="9">
+        <v>1</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="11">
+        <v>275297</v>
+      </c>
+      <c r="D3" s="12">
+        <v>26008310.899999999</v>
+      </c>
+      <c r="E3" s="13">
+        <v>0.25795776924557839</v>
+      </c>
+      <c r="F3" s="13" t="s">
         <v>11</v>
       </c>
+      <c r="G3" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="H3" s="13">
+        <v>0.24315050770944147</v>
+      </c>
+      <c r="I3" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="J3" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="K3" s="15">
+        <v>89.050679433922411</v>
+      </c>
+      <c r="L3" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="M3" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="N3" s="17">
+        <v>0.13189999999999999</v>
+      </c>
+      <c r="O3" s="6"/>
+      <c r="P3" s="17" t="e">
+        <f>+#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="Q3" s="17" t="e">
+        <f>+#REF!</f>
+        <v>#REF!</v>
+      </c>
     </row>
-    <row r="3" spans="2:15">
-      <c r="B3" s="20">
-        <v>1</v>
-      </c>
-      <c r="C3" s="27" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" s="21">
-        <v>568604</v>
-      </c>
-      <c r="E3" s="22">
-        <v>42414252.5</v>
-      </c>
-      <c r="F3" s="23">
-        <v>0.24126457077333258</v>
-      </c>
-      <c r="G3" s="23">
-        <v>0.25318457456676596</v>
-      </c>
-      <c r="H3" s="24">
-        <v>-1.1920003793433387E-2</v>
-      </c>
-      <c r="I3" s="23">
-        <v>0.24263134190564833</v>
-      </c>
-      <c r="J3" s="23">
-        <v>0.25419954069479184</v>
-      </c>
-      <c r="K3" s="24">
-        <v>-1.1568198789143502E-2</v>
-      </c>
-      <c r="L3" s="25">
-        <v>75.016233671565203</v>
-      </c>
-      <c r="M3" s="25">
-        <v>73.656116886269842</v>
-      </c>
-      <c r="N3" s="26">
-        <v>1.3601167852953608</v>
-      </c>
-      <c r="O3" s="29">
-        <v>8.0805129721496088E-2</v>
+    <row r="4" spans="1:17">
+      <c r="A4" s="18">
+        <v>2</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="20">
+        <v>119161</v>
+      </c>
+      <c r="D4" s="21">
+        <v>9130529.5</v>
+      </c>
+      <c r="E4" s="22">
+        <v>0.23748541888705196</v>
+      </c>
+      <c r="F4" s="22">
+        <v>0.23229166003552171</v>
+      </c>
+      <c r="G4" s="23">
+        <v>5.1937588515302557E-3</v>
+      </c>
+      <c r="H4" s="22">
+        <v>0.23108451705895042</v>
+      </c>
+      <c r="I4" s="22">
+        <v>0.23522530648228221</v>
+      </c>
+      <c r="J4" s="23">
+        <v>-4.1407894233317921E-3</v>
+      </c>
+      <c r="K4" s="24">
+        <v>74.558252941800063</v>
+      </c>
+      <c r="L4" s="24">
+        <v>76.993614688955873</v>
+      </c>
+      <c r="M4" s="25">
+        <v>-2.4353617471558096</v>
+      </c>
+      <c r="N4" s="17">
+        <v>9.5899999999999999E-2</v>
+      </c>
+      <c r="O4" s="6"/>
+      <c r="P4" s="17" t="e">
+        <f t="shared" ref="P4:Q12" si="0">+#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="Q4" s="17" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
       </c>
     </row>
-    <row r="4" spans="2:15">
-      <c r="B4" s="20">
-        <v>2</v>
-      </c>
-      <c r="C4" s="27" t="s">
+    <row r="5" spans="1:17">
+      <c r="A5" s="18">
+        <v>3</v>
+      </c>
+      <c r="B5" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="20">
+        <v>81468</v>
+      </c>
+      <c r="D5" s="21">
+        <v>6354965.9000000004</v>
+      </c>
+      <c r="E5" s="22">
+        <v>0.24630529778563362</v>
+      </c>
+      <c r="F5" s="22">
+        <v>0.23608338226658837</v>
+      </c>
+      <c r="G5" s="23">
+        <v>1.0221915519045249E-2</v>
+      </c>
+      <c r="H5" s="22">
+        <v>0.24288438746775964</v>
+      </c>
+      <c r="I5" s="22">
+        <v>0.23579982138623018</v>
+      </c>
+      <c r="J5" s="23">
+        <v>7.0845660815294642E-3</v>
+      </c>
+      <c r="K5" s="24">
+        <v>76.92225655337387</v>
+      </c>
+      <c r="L5" s="24">
+        <v>76.892840857273143</v>
+      </c>
+      <c r="M5" s="25">
+        <v>2.9415696100727473E-2</v>
+      </c>
+      <c r="N5" s="17">
+        <v>0.11219999999999999</v>
+      </c>
+      <c r="O5" s="6"/>
+      <c r="P5" s="17" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
+      </c>
+      <c r="Q5" s="17" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17">
+      <c r="A6" s="18">
+        <v>4</v>
+      </c>
+      <c r="B6" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="20">
+        <v>60453</v>
+      </c>
+      <c r="D6" s="21">
+        <v>4811613.3</v>
+      </c>
+      <c r="E6" s="22">
+        <v>0.29753692951549138</v>
+      </c>
+      <c r="F6" s="22">
+        <v>0.2407321492660125</v>
+      </c>
+      <c r="G6" s="26">
+        <v>5.6804780249478881E-2</v>
+      </c>
+      <c r="H6" s="22">
+        <v>0.29048988620926791</v>
+      </c>
+      <c r="I6" s="22">
+        <v>0.23834970398259894</v>
+      </c>
+      <c r="J6" s="26">
+        <v>5.2140182226668969E-2</v>
+      </c>
+      <c r="K6" s="24">
+        <v>77.707510980152335</v>
+      </c>
+      <c r="L6" s="24">
+        <v>78.521435584160571</v>
+      </c>
+      <c r="M6" s="27">
+        <v>-0.81392460400823552</v>
+      </c>
+      <c r="N6" s="17">
+        <v>0.1076</v>
+      </c>
+      <c r="O6" s="6"/>
+      <c r="P6" s="17" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
+      </c>
+      <c r="Q6" s="17" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17">
+      <c r="A7" s="18">
+        <v>5</v>
+      </c>
+      <c r="B7" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" s="20">
+        <v>19553</v>
+      </c>
+      <c r="D7" s="21">
+        <v>1458642.2</v>
+      </c>
+      <c r="E7" s="22">
+        <v>0.29325423208714774</v>
+      </c>
+      <c r="F7" s="22">
+        <v>0.27203092733996059</v>
+      </c>
+      <c r="G7" s="23">
+        <v>2.1223304747187144E-2</v>
+      </c>
+      <c r="H7" s="22">
+        <v>0.29044134332600552</v>
+      </c>
+      <c r="I7" s="22">
+        <v>0.25774763658097094</v>
+      </c>
+      <c r="J7" s="23">
+        <v>3.2693706745034579E-2</v>
+      </c>
+      <c r="K7" s="24">
+        <v>73.883850715033134</v>
+      </c>
+      <c r="L7" s="24">
+        <v>71.062317945096652</v>
+      </c>
+      <c r="M7" s="25">
+        <v>2.8215327699364821</v>
+      </c>
+      <c r="N7" s="17">
+        <v>8.7999999999999995E-2</v>
+      </c>
+      <c r="O7" s="6"/>
+      <c r="P7" s="17" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
+      </c>
+      <c r="Q7" s="17" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17">
+      <c r="A8" s="18">
+        <v>6</v>
+      </c>
+      <c r="B8" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="20">
+        <v>8879</v>
+      </c>
+      <c r="D8" s="21">
+        <v>919593.6</v>
+      </c>
+      <c r="E8" s="22">
+        <v>0.22862935015204414</v>
+      </c>
+      <c r="F8" s="22">
+        <v>0.22610502455610124</v>
+      </c>
+      <c r="G8" s="23">
+        <v>2.5243255959429001E-3</v>
+      </c>
+      <c r="H8" s="22">
+        <v>0.23339331635191893</v>
+      </c>
+      <c r="I8" s="22">
+        <v>0.22106198361663074</v>
+      </c>
+      <c r="J8" s="23">
+        <v>1.2331332735288192E-2</v>
+      </c>
+      <c r="K8" s="24">
+        <v>105.72758620689655</v>
+      </c>
+      <c r="L8" s="24">
+        <v>94.372598162071853</v>
+      </c>
+      <c r="M8" s="25">
+        <v>11.354988044824694</v>
+      </c>
+      <c r="N8" s="17">
+        <v>6.8900000000000003E-2</v>
+      </c>
+      <c r="O8" s="6"/>
+      <c r="P8" s="17" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
+      </c>
+      <c r="Q8" s="17" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17">
+      <c r="A9" s="18">
+        <v>7</v>
+      </c>
+      <c r="B9" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="20">
+        <v>5921</v>
+      </c>
+      <c r="D9" s="21">
+        <v>521198.1</v>
+      </c>
+      <c r="E9" s="22">
+        <v>0.30738051004897821</v>
+      </c>
+      <c r="F9" s="22">
+        <v>0.28453060896146731</v>
+      </c>
+      <c r="G9" s="23">
+        <v>2.2849901087510893E-2</v>
+      </c>
+      <c r="H9" s="22">
+        <v>0.29529462981541954</v>
+      </c>
+      <c r="I9" s="22">
+        <v>0.27403556372142301</v>
+      </c>
+      <c r="J9" s="23">
+        <v>2.1259066093996526E-2</v>
+      </c>
+      <c r="K9" s="24">
+        <v>84.564285714285717</v>
+      </c>
+      <c r="L9" s="24">
+        <v>81.519932145886344</v>
+      </c>
+      <c r="M9" s="25">
+        <v>3.044353568399373</v>
+      </c>
+      <c r="N9" s="17">
+        <v>0.1074</v>
+      </c>
+      <c r="O9" s="6"/>
+      <c r="P9" s="17" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
+      </c>
+      <c r="Q9" s="17" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17">
+      <c r="A10" s="18">
+        <v>8</v>
+      </c>
+      <c r="B10" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" s="20">
+        <v>3667</v>
+      </c>
+      <c r="D10" s="21">
+        <v>322577</v>
+      </c>
+      <c r="E10" s="22">
+        <v>0.34333242432506134</v>
+      </c>
+      <c r="F10" s="22">
+        <v>0.29532775453277543</v>
+      </c>
+      <c r="G10" s="23">
+        <v>4.8004669792285903E-2</v>
+      </c>
+      <c r="H10" s="22">
+        <v>0.33414657585630719</v>
+      </c>
+      <c r="I10" s="22">
+        <v>0.3043538337880905</v>
+      </c>
+      <c r="J10" s="23">
+        <v>2.9792742068216693E-2</v>
+      </c>
+      <c r="K10" s="24">
+        <v>85.61397934868944</v>
+      </c>
+      <c r="L10" s="24">
+        <v>88.807556080283348</v>
+      </c>
+      <c r="M10" s="25">
+        <v>-3.1935767315939074</v>
+      </c>
+      <c r="N10" s="17">
+        <v>0.1386</v>
+      </c>
+      <c r="O10" s="6"/>
+      <c r="P10" s="17" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
+      </c>
+      <c r="Q10" s="17" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17">
+      <c r="A11" s="18">
+        <v>9</v>
+      </c>
+      <c r="B11" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="20">
+        <v>2510</v>
+      </c>
+      <c r="D11" s="21">
+        <v>201596.6</v>
+      </c>
+      <c r="E11" s="22">
+        <v>0.32629482071713145</v>
+      </c>
+      <c r="F11" s="22">
+        <v>0.35486056226713336</v>
+      </c>
+      <c r="G11" s="26">
+        <v>-2.8565741550001911E-2</v>
+      </c>
+      <c r="H11" s="22">
+        <v>0.31533765946449493</v>
+      </c>
+      <c r="I11" s="22">
+        <v>0.34724110464576929</v>
+      </c>
+      <c r="J11" s="26">
+        <v>-3.1903445181274359E-2</v>
+      </c>
+      <c r="K11" s="24">
+        <v>77.620268620268618</v>
+      </c>
+      <c r="L11" s="24">
+        <v>75.981546293350306</v>
+      </c>
+      <c r="M11" s="27">
+        <v>1.6387223269183124</v>
+      </c>
+      <c r="N11" s="17">
+        <v>7.4499999999999997E-2</v>
+      </c>
+      <c r="O11" s="6"/>
+      <c r="P11" s="17" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
+      </c>
+      <c r="Q11" s="17" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17">
+      <c r="A12" s="18">
+        <v>10</v>
+      </c>
+      <c r="B12" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="20">
+        <v>1631</v>
+      </c>
+      <c r="D12" s="21">
+        <v>131369</v>
+      </c>
+      <c r="E12" s="22">
+        <v>0.24586143470263641</v>
+      </c>
+      <c r="F12" s="22">
+        <v>0.30859758090879374</v>
+      </c>
+      <c r="G12" s="26">
+        <v>-6.2736146206157334E-2</v>
+      </c>
+      <c r="H12" s="22">
+        <v>0.21359681507813869</v>
+      </c>
+      <c r="I12" s="22">
+        <v>0.29520473953153398</v>
+      </c>
+      <c r="J12" s="26">
+        <v>-8.1607924453395292E-2</v>
+      </c>
+      <c r="K12" s="24">
+        <v>69.975062344139644</v>
+      </c>
+      <c r="L12" s="24">
+        <v>72.94809322033899</v>
+      </c>
+      <c r="M12" s="27">
+        <v>-2.9730308761993456</v>
+      </c>
+      <c r="N12" s="17">
+        <v>7.3300000000000004E-2</v>
+      </c>
+      <c r="O12" s="6"/>
+      <c r="P12" s="17" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
+      </c>
+      <c r="Q12" s="17" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17">
+      <c r="A13" s="28"/>
+      <c r="B13" s="29" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" s="30"/>
+      <c r="D13" s="31"/>
+      <c r="E13" s="32">
+        <v>0</v>
+      </c>
+      <c r="F13" s="32"/>
+      <c r="G13" s="33"/>
+      <c r="H13" s="32">
+        <v>0</v>
+      </c>
+      <c r="I13" s="32"/>
+      <c r="J13" s="33"/>
+      <c r="K13" s="34">
+        <f>+IFERROR(D13/C13,0)</f>
+        <v>0</v>
+      </c>
+      <c r="L13" s="34"/>
+      <c r="M13" s="35"/>
+      <c r="N13" s="32"/>
+      <c r="O13" s="6"/>
+      <c r="P13" s="32"/>
+      <c r="Q13" s="32"/>
+    </row>
+    <row r="14" spans="1:17" ht="3" customHeight="1">
+      <c r="A14" s="36"/>
+      <c r="B14" s="37"/>
+      <c r="C14" s="38"/>
+      <c r="D14" s="39"/>
+      <c r="E14" s="40"/>
+      <c r="F14" s="40"/>
+      <c r="G14" s="41"/>
+      <c r="H14" s="40"/>
+      <c r="I14" s="40"/>
+      <c r="J14" s="41"/>
+      <c r="K14" s="42"/>
+      <c r="L14" s="42"/>
+      <c r="M14" s="43"/>
+      <c r="N14" s="44"/>
+      <c r="O14" s="6"/>
+      <c r="P14" s="44"/>
+      <c r="Q14" s="44"/>
+    </row>
+    <row r="15" spans="1:17">
+      <c r="A15" s="1"/>
+      <c r="B15" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="21">
-        <v>226617</v>
-      </c>
-      <c r="E4" s="22">
-        <v>20595164.899999999</v>
-      </c>
-      <c r="F4" s="23">
-        <v>0.25855959614680274</v>
-      </c>
-      <c r="G4" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="H4" s="24" t="s">
-        <v>14</v>
-      </c>
-      <c r="I4" s="23">
-        <v>0.23871335936717847</v>
-      </c>
-      <c r="J4" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="K4" s="24" t="s">
-        <v>14</v>
-      </c>
-      <c r="L4" s="25">
-        <v>83.905195071167697</v>
-      </c>
-      <c r="M4" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="N4" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="O4" s="29">
-        <v>8.8980882337308526E-2</v>
+      <c r="C15" s="45">
+        <v>589811.66999999993</v>
+      </c>
+      <c r="D15" s="46">
+        <v>50661176.364999995</v>
+      </c>
+      <c r="E15" s="47">
+        <v>0.25368097582741966</v>
+      </c>
+      <c r="F15" s="47">
+        <v>0.24273395902316994</v>
+      </c>
+      <c r="G15" s="48">
+        <v>1.0947016804249726E-2</v>
+      </c>
+      <c r="H15" s="47">
+        <v>0.24446007551763255</v>
+      </c>
+      <c r="I15" s="47">
+        <v>0.24135265824962174</v>
+      </c>
+      <c r="J15" s="48">
+        <v>3.1074172680108092E-3</v>
+      </c>
+      <c r="K15" s="49">
+        <v>82.771714430839978</v>
+      </c>
+      <c r="L15" s="49">
+        <v>77.556965376063246</v>
+      </c>
+      <c r="M15" s="50">
+        <v>5.2147490547767319</v>
+      </c>
+      <c r="N15" s="51">
+        <v>0.1133</v>
+      </c>
+      <c r="O15" s="6"/>
+      <c r="P15" s="51" t="e">
+        <f>+#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="Q15" s="51" t="e">
+        <f>+#REF!</f>
+        <v>#REF!</v>
       </c>
     </row>
-    <row r="5" spans="2:15">
-      <c r="B5" s="20">
-        <v>3</v>
-      </c>
-      <c r="C5" s="27" t="s">
+    <row r="16" spans="1:17" ht="3" customHeight="1">
+      <c r="A16" s="37"/>
+      <c r="B16" s="37"/>
+      <c r="C16" s="37"/>
+      <c r="D16" s="37"/>
+      <c r="E16" s="37"/>
+      <c r="F16" s="37"/>
+      <c r="G16" s="37"/>
+      <c r="H16" s="37"/>
+      <c r="I16" s="37"/>
+      <c r="J16" s="37"/>
+      <c r="K16" s="37"/>
+      <c r="L16" s="37"/>
+      <c r="M16" s="37"/>
+      <c r="N16" s="52"/>
+      <c r="O16" s="53"/>
+      <c r="P16" s="53"/>
+      <c r="Q16" s="53"/>
+    </row>
+    <row r="17" spans="1:17">
+      <c r="A17" s="54"/>
+      <c r="B17" s="55">
+        <v>2025</v>
+      </c>
+      <c r="C17" s="56">
+        <v>467675.09615384613</v>
+      </c>
+      <c r="D17" s="57">
+        <v>35298385.945429988</v>
+      </c>
+      <c r="E17" s="58">
+        <v>0.25655027189528562</v>
+      </c>
+      <c r="F17" s="58"/>
+      <c r="G17" s="59"/>
+      <c r="H17" s="58">
+        <v>0.23133410456808196</v>
+      </c>
+      <c r="I17" s="58"/>
+      <c r="J17" s="59"/>
+      <c r="K17" s="60">
+        <v>68.057781385151287</v>
+      </c>
+      <c r="L17" s="60"/>
+      <c r="M17" s="61"/>
+      <c r="N17" s="51"/>
+      <c r="O17" s="6"/>
+      <c r="P17" s="51"/>
+      <c r="Q17" s="51"/>
+    </row>
+    <row r="18" spans="1:17" ht="3" customHeight="1">
+      <c r="A18" s="62"/>
+      <c r="B18" s="62"/>
+      <c r="C18" s="62"/>
+      <c r="D18" s="62"/>
+      <c r="E18" s="62"/>
+      <c r="F18" s="62"/>
+      <c r="G18" s="62"/>
+      <c r="H18" s="62"/>
+      <c r="I18" s="62"/>
+      <c r="J18" s="62"/>
+      <c r="K18" s="62"/>
+      <c r="L18" s="62"/>
+      <c r="M18" s="62"/>
+      <c r="N18" s="63"/>
+      <c r="O18" s="63"/>
+      <c r="P18" s="63"/>
+      <c r="Q18" s="63"/>
+    </row>
+    <row r="19" spans="1:17">
+      <c r="A19" s="54"/>
+      <c r="B19" s="64" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="21">
-        <v>235514</v>
-      </c>
-      <c r="E5" s="22">
-        <v>17150595</v>
-      </c>
-      <c r="F5" s="23">
-        <v>0.24831220224700018</v>
-      </c>
-      <c r="G5" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="H5" s="24" t="s">
-        <v>14</v>
-      </c>
-      <c r="I5" s="23">
-        <v>0.23014705903789343</v>
-      </c>
-      <c r="J5" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="K5" s="24" t="s">
-        <v>14</v>
-      </c>
-      <c r="L5" s="25">
-        <v>67.494724782407957</v>
-      </c>
-      <c r="M5" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="N5" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="O5" s="29">
-        <v>0.16780871052344634</v>
-      </c>
+      <c r="C19" s="65">
+        <f>+C15/C17-1</f>
+        <v>0.26115689043655177</v>
+      </c>
+      <c r="D19" s="66">
+        <f>+D15/D17-1</f>
+        <v>0.43522642772732767</v>
+      </c>
+      <c r="E19" s="66">
+        <f>+E15-E17</f>
+        <v>-2.8692960678659563E-3</v>
+      </c>
+      <c r="F19" s="58"/>
+      <c r="G19" s="59"/>
+      <c r="H19" s="66">
+        <f>+H15-H17</f>
+        <v>1.3125970949550592E-2</v>
+      </c>
+      <c r="I19" s="58"/>
+      <c r="J19" s="59"/>
+      <c r="K19" s="67">
+        <f>+K15-K17</f>
+        <v>14.713933045688691</v>
+      </c>
+      <c r="L19" s="60"/>
+      <c r="M19" s="61"/>
+      <c r="N19" s="51"/>
+      <c r="O19" s="6"/>
+      <c r="P19" s="51"/>
+      <c r="Q19" s="51"/>
     </row>
-    <row r="6" spans="2:15">
-      <c r="B6" s="20">
-        <v>4</v>
-      </c>
-      <c r="C6" s="27" t="s">
+    <row r="20" spans="1:17" ht="3" customHeight="1">
+      <c r="A20" s="52"/>
+      <c r="B20" s="68"/>
+      <c r="C20" s="69"/>
+      <c r="D20" s="70"/>
+      <c r="E20" s="71"/>
+      <c r="F20" s="71"/>
+      <c r="G20" s="72"/>
+      <c r="H20" s="71"/>
+      <c r="I20" s="71"/>
+      <c r="J20" s="72"/>
+      <c r="K20" s="73"/>
+      <c r="L20" s="73"/>
+      <c r="M20" s="74"/>
+      <c r="N20" s="71"/>
+      <c r="O20" s="52"/>
+      <c r="P20" s="75"/>
+      <c r="Q20" s="75"/>
+    </row>
+    <row r="21" spans="1:17">
+      <c r="A21" s="54"/>
+      <c r="B21" s="55" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="21">
-        <v>185096</v>
-      </c>
-      <c r="E6" s="22">
-        <v>13808434</v>
-      </c>
-      <c r="F6" s="23">
-        <v>0.20468297532091456</v>
-      </c>
-      <c r="G6" s="23">
-        <v>0.25031455282292869</v>
-      </c>
-      <c r="H6" s="24">
-        <v>-4.5631577502014131E-2</v>
-      </c>
-      <c r="I6" s="23">
-        <v>0.18824408328996611</v>
-      </c>
-      <c r="J6" s="23">
-        <v>0.23416634481727558</v>
-      </c>
-      <c r="K6" s="24">
-        <v>-4.5922261527309466E-2</v>
-      </c>
-      <c r="L6" s="25">
-        <v>68.609935068362986</v>
-      </c>
-      <c r="M6" s="25">
-        <v>71.131347078334812</v>
-      </c>
-      <c r="N6" s="26">
-        <v>-2.5214120099718258</v>
-      </c>
-      <c r="O6" s="29">
-        <v>9.7548290085534339E-2</v>
-      </c>
+      <c r="C21" s="56">
+        <v>443168.03448275861</v>
+      </c>
+      <c r="D21" s="57">
+        <v>35546986.372068577</v>
+      </c>
+      <c r="E21" s="58">
+        <v>0.25850683398443169</v>
+      </c>
+      <c r="F21" s="58"/>
+      <c r="G21" s="59"/>
+      <c r="H21" s="58">
+        <v>0.24600195973901218</v>
+      </c>
+      <c r="I21" s="58"/>
+      <c r="J21" s="59"/>
+      <c r="K21" s="60">
+        <v>76.330990576700401</v>
+      </c>
+      <c r="L21" s="60"/>
+      <c r="M21" s="61"/>
+      <c r="N21" s="51"/>
+      <c r="O21" s="6"/>
+      <c r="P21" s="51"/>
+      <c r="Q21" s="51"/>
     </row>
-    <row r="7" spans="2:15">
-      <c r="B7" s="20">
-        <v>5</v>
-      </c>
-      <c r="C7" s="27" t="s">
+    <row r="22" spans="1:17" ht="3" customHeight="1">
+      <c r="A22" s="62"/>
+      <c r="B22" s="62"/>
+      <c r="C22" s="62"/>
+      <c r="D22" s="62"/>
+      <c r="E22" s="62"/>
+      <c r="F22" s="62"/>
+      <c r="G22" s="62"/>
+      <c r="H22" s="62"/>
+      <c r="I22" s="62"/>
+      <c r="J22" s="62"/>
+      <c r="K22" s="62"/>
+      <c r="L22" s="62"/>
+      <c r="M22" s="62"/>
+      <c r="N22" s="63"/>
+      <c r="O22" s="63"/>
+      <c r="P22" s="63"/>
+      <c r="Q22" s="63"/>
+    </row>
+    <row r="23" spans="1:17">
+      <c r="A23" s="54"/>
+      <c r="B23" s="64" t="s">
         <v>17</v>
       </c>
-      <c r="D7" s="21">
-        <v>141437</v>
-      </c>
-      <c r="E7" s="22">
-        <v>10021462.1</v>
-      </c>
-      <c r="F7" s="23">
-        <v>0.2594158529946195</v>
-      </c>
-      <c r="G7" s="23">
-        <v>0.21441581709620106</v>
-      </c>
-      <c r="H7" s="24">
-        <v>4.5000035898418445E-2</v>
-      </c>
-      <c r="I7" s="23">
-        <v>0.25818887246003758</v>
-      </c>
-      <c r="J7" s="23">
-        <v>0.20431663495688601</v>
-      </c>
-      <c r="K7" s="24">
-        <v>5.3872237503151565E-2</v>
-      </c>
-      <c r="L7" s="25">
-        <v>70.519473440353224</v>
-      </c>
-      <c r="M7" s="25">
-        <v>70.530140365506213</v>
-      </c>
-      <c r="N7" s="26">
-        <v>-1.0666925152989393E-2</v>
-      </c>
-      <c r="O7" s="29">
-        <v>9.6121703683909945E-2</v>
-      </c>
+      <c r="C23" s="65">
+        <f>+C15/C21-1</f>
+        <v>0.33089849471746247</v>
+      </c>
+      <c r="D23" s="66">
+        <f>+D15/D21-1</f>
+        <v>0.42518906763943165</v>
+      </c>
+      <c r="E23" s="66">
+        <f>+E15-E21</f>
+        <v>-4.8258581570120307E-3</v>
+      </c>
+      <c r="F23" s="58"/>
+      <c r="G23" s="59"/>
+      <c r="H23" s="66">
+        <f>+H15-H21</f>
+        <v>-1.5418842213796302E-3</v>
+      </c>
+      <c r="I23" s="58"/>
+      <c r="J23" s="59"/>
+      <c r="K23" s="67">
+        <f>+K15-K21</f>
+        <v>6.440723854139577</v>
+      </c>
+      <c r="L23" s="60"/>
+      <c r="M23" s="61"/>
+      <c r="N23" s="51"/>
+      <c r="O23" s="6"/>
+      <c r="P23" s="51"/>
+      <c r="Q23" s="51"/>
     </row>
-    <row r="8" spans="2:15">
-      <c r="B8" s="20">
-        <v>6</v>
-      </c>
-      <c r="C8" s="27" t="s">
-        <v>18</v>
-      </c>
-      <c r="D8" s="21">
-        <v>123441</v>
-      </c>
-      <c r="E8" s="22">
-        <v>9145521.8000000007</v>
-      </c>
-      <c r="F8" s="23">
-        <v>0.27488435770935105</v>
-      </c>
-      <c r="G8" s="23">
-        <v>0.20291049206945438</v>
-      </c>
-      <c r="H8" s="24">
-        <v>7.1973865639896661E-2</v>
-      </c>
-      <c r="I8" s="23">
-        <v>0.2795543060211173</v>
-      </c>
-      <c r="J8" s="23">
-        <v>0.18930906335433073</v>
-      </c>
-      <c r="K8" s="24">
-        <v>9.0245242666786574E-2</v>
-      </c>
-      <c r="L8" s="25">
-        <v>75.346870211010256</v>
-      </c>
-      <c r="M8" s="25">
-        <v>72.862932441578081</v>
-      </c>
-      <c r="N8" s="26">
-        <v>2.483937769432174</v>
-      </c>
-      <c r="O8" s="29">
-        <v>8.2715582911816687E-2</v>
-      </c>
-    </row>
-    <row r="9" spans="2:15">
-      <c r="B9" s="20">
-        <v>7</v>
-      </c>
-      <c r="C9" s="27" t="s">
-        <v>19</v>
-      </c>
-      <c r="D9" s="21">
-        <v>100094</v>
-      </c>
-      <c r="E9" s="22">
-        <v>7559446.9000000004</v>
-      </c>
-      <c r="F9" s="23">
-        <v>0.21395887865406518</v>
-      </c>
-      <c r="G9" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="H9" s="24" t="s">
-        <v>14</v>
-      </c>
-      <c r="I9" s="23">
-        <v>0.20058848485330322</v>
-      </c>
-      <c r="J9" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="K9" s="24" t="s">
-        <v>14</v>
-      </c>
-      <c r="L9" s="25">
-        <v>70.803978333955925</v>
-      </c>
-      <c r="M9" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="N9" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="O9" s="29">
-        <v>2.868282151318759E-2</v>
-      </c>
-    </row>
-    <row r="10" spans="2:15">
-      <c r="B10" s="20">
-        <v>8</v>
-      </c>
-      <c r="C10" s="27" t="s">
-        <v>20</v>
-      </c>
-      <c r="D10" s="21">
-        <v>44385</v>
-      </c>
-      <c r="E10" s="22">
-        <v>4602087.5</v>
-      </c>
-      <c r="F10" s="23">
-        <v>0.24301002590965418</v>
-      </c>
-      <c r="G10" s="23">
-        <v>0.24525427995971802</v>
-      </c>
-      <c r="H10" s="24">
-        <v>-2.244254050063843E-3</v>
-      </c>
-      <c r="I10" s="23">
-        <v>0.27272080333109705</v>
-      </c>
-      <c r="J10" s="23">
-        <v>0.24926501201454929</v>
-      </c>
-      <c r="K10" s="24">
-        <v>2.3455791316547764E-2</v>
-      </c>
-      <c r="L10" s="25">
-        <v>116.36241424068237</v>
-      </c>
-      <c r="M10" s="25">
-        <v>106.96068367294565</v>
-      </c>
-      <c r="N10" s="26">
-        <v>9.4017305677367204</v>
-      </c>
-      <c r="O10" s="29">
-        <v>0.15519647764716038</v>
-      </c>
-    </row>
-    <row r="11" spans="2:15">
-      <c r="B11" s="20">
-        <v>9</v>
-      </c>
-      <c r="C11" s="27" t="s">
-        <v>21</v>
-      </c>
-      <c r="D11" s="21">
-        <v>60503</v>
-      </c>
-      <c r="E11" s="22">
-        <v>3844754</v>
-      </c>
-      <c r="F11" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="G11" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="H11" s="24" t="s">
-        <v>14</v>
-      </c>
-      <c r="I11" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="J11" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="K11" s="24" t="s">
-        <v>14</v>
-      </c>
-      <c r="L11" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="M11" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="N11" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="O11" s="29" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="12" spans="2:15">
-      <c r="B12" s="20">
-        <v>10</v>
-      </c>
-      <c r="C12" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="D12" s="21">
-        <v>34033</v>
-      </c>
-      <c r="E12" s="22">
-        <v>3730372</v>
-      </c>
-      <c r="F12" s="23">
-        <v>0.23897393706108777</v>
-      </c>
-      <c r="G12" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="H12" s="24" t="s">
-        <v>14</v>
-      </c>
-      <c r="I12" s="23">
-        <v>0.26703315379806625</v>
-      </c>
-      <c r="J12" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="K12" s="24" t="s">
-        <v>14</v>
-      </c>
-      <c r="L12" s="25">
-        <v>122.48038854051396</v>
-      </c>
-      <c r="M12" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="N12" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="O12" s="29">
-        <v>0.11815210285465243</v>
-      </c>
-    </row>
-    <row r="13" spans="2:15">
-      <c r="B13" s="4"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
-      <c r="H13" s="16"/>
-      <c r="I13" s="5"/>
-      <c r="J13" s="5"/>
-      <c r="K13" s="16"/>
-      <c r="L13" s="6"/>
-      <c r="M13" s="6"/>
-      <c r="N13" s="18"/>
-      <c r="O13" s="30">
-        <v>6.3725027075031401E-2</v>
-      </c>
-    </row>
-    <row r="14" spans="2:15">
-      <c r="B14" s="9"/>
-      <c r="C14" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="D14" s="13">
-        <v>1961117</v>
-      </c>
-      <c r="E14" s="15">
-        <v>151343727.5</v>
-      </c>
-      <c r="F14" s="11">
-        <v>0.2382218908917724</v>
-      </c>
-      <c r="G14" s="11">
-        <v>0.23290443584065537</v>
-      </c>
-      <c r="H14" s="17">
-        <v>5.317455051117026E-3</v>
-      </c>
-      <c r="I14" s="11">
-        <v>0.2334274771975601</v>
-      </c>
-      <c r="J14" s="11">
-        <v>0.22698895568963723</v>
-      </c>
-      <c r="K14" s="17">
-        <v>6.438521507922873E-3</v>
-      </c>
-      <c r="L14" s="12">
-        <v>75.619052358721774</v>
-      </c>
-      <c r="M14" s="12">
-        <v>75.02227396146715</v>
-      </c>
-      <c r="N14" s="19">
-        <v>0.59677839725462434</v>
-      </c>
-      <c r="O14" s="30">
-        <v>8.0889355068152743E-2</v>
-      </c>
-    </row>
-    <row r="32" ht="9" customHeight="1"/>
+    <row r="32" spans="1:17" ht="9" customHeight="1"/>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="P1:Q1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="G3:G12 J3:J12 M3:M12">
+    <cfRule type="cellIs" dxfId="23" priority="22" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N3:N12">
+    <cfRule type="cellIs" dxfId="22" priority="24" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P3:Q12">
+    <cfRule type="cellIs" dxfId="21" priority="23" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C19:E19">
+    <cfRule type="cellIs" dxfId="20" priority="18" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C23:E23">
+    <cfRule type="cellIs" dxfId="19" priority="10" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G13:G15 J13:J15 M13:M15">
+    <cfRule type="cellIs" dxfId="18" priority="19" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G17">
+    <cfRule type="cellIs" dxfId="17" priority="3" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G20:G21">
+    <cfRule type="cellIs" dxfId="16" priority="12" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G19:H19">
+    <cfRule type="cellIs" dxfId="15" priority="17" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G23:H23">
+    <cfRule type="cellIs" dxfId="14" priority="9" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J17">
+    <cfRule type="cellIs" dxfId="13" priority="2" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J20:J21">
+    <cfRule type="cellIs" dxfId="12" priority="11" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J19:K19">
+    <cfRule type="cellIs" dxfId="11" priority="16" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J23:K23">
+    <cfRule type="cellIs" dxfId="10" priority="8" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M20">
+    <cfRule type="cellIs" dxfId="9" priority="13" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M17:N17">
+    <cfRule type="cellIs" dxfId="8" priority="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M19:N19">
+    <cfRule type="cellIs" dxfId="7" priority="14" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M21:N21">
+    <cfRule type="cellIs" dxfId="6" priority="5" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M23:N23">
+    <cfRule type="cellIs" dxfId="5" priority="4" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N14:N15">
+    <cfRule type="cellIs" dxfId="4" priority="21" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P14:Q15">
+    <cfRule type="cellIs" dxfId="3" priority="20" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P17:Q17">
+    <cfRule type="cellIs" dxfId="2" priority="15" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P19:Q21">
+    <cfRule type="cellIs" dxfId="1" priority="7" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P23:Q23">
+    <cfRule type="cellIs" dxfId="0" priority="6" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
